--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.25468849719166</v>
+        <v>2.803886880793645</v>
       </c>
       <c r="D2" t="n">
-        <v>14.44921341897905</v>
+        <v>2.347997180584096</v>
       </c>
       <c r="E2" t="n">
-        <v>10.67590727856003</v>
+        <v>1.734834932766005</v>
       </c>
       <c r="F2" t="n">
-        <v>8.497974531522118</v>
+        <v>1.380920861372344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.22244034004461</v>
+        <v>8.161146555257249</v>
       </c>
       <c r="D3" t="n">
-        <v>27.89517709435813</v>
+        <v>4.532966277833197</v>
       </c>
       <c r="E3" t="n">
-        <v>10.67590727856003</v>
+        <v>1.734834932766005</v>
       </c>
       <c r="F3" t="n">
-        <v>8.497974531522118</v>
+        <v>1.380920861372344</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.62851534706682</v>
+        <v>6.439633743898358</v>
       </c>
       <c r="D4" t="n">
-        <v>37.52487746865523</v>
+        <v>6.097792588656475</v>
       </c>
       <c r="E4" t="n">
-        <v>10.67590727856003</v>
+        <v>1.734834932766005</v>
       </c>
       <c r="F4" t="n">
-        <v>8.497974531522118</v>
+        <v>1.380920861372344</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.46885349412349</v>
+        <v>6.088688692795067</v>
       </c>
       <c r="D5" t="n">
-        <v>37.56625622501335</v>
+        <v>6.104516636564671</v>
       </c>
       <c r="E5" t="n">
-        <v>10.67590727856003</v>
+        <v>1.734834932766005</v>
       </c>
       <c r="F5" t="n">
-        <v>8.497974531522118</v>
+        <v>1.380920861372344</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.2443776975595</v>
+        <v>6.052211375853419</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15913547189666</v>
+        <v>5.063359514183208</v>
       </c>
       <c r="E6" t="n">
-        <v>10.67590727856003</v>
+        <v>1.734834932766005</v>
       </c>
       <c r="F6" t="n">
-        <v>8.497974531522118</v>
+        <v>1.380920861372344</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
